--- a/advanced-prompting/csv/gpt-4o-mini-2024-07-18_FT-150_PV1_new30.xlsx
+++ b/advanced-prompting/csv/gpt-4o-mini-2024-07-18_FT-150_PV1_new30.xlsx
@@ -464,7 +464,9 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -482,7 +484,9 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -518,7 +522,9 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PV008448-PV008641, PV407014-PV407203, PV419497-PV419583</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -536,7 +542,9 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe
+```
+```</t>
         </is>
       </c>
     </row>
@@ -554,7 +562,9 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe</t>
+          <t>2022–2024
+```
+```</t>
         </is>
       </c>
     </row>
@@ -572,7 +582,9 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2022–2024</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -590,7 +602,9 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -608,7 +622,9 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma, DBS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -626,7 +642,9 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -644,7 +662,9 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Plasma, DBS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -662,7 +682,9 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>488
+```
+```</t>
         </is>
       </c>
     </row>
@@ -680,7 +702,9 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -698,7 +722,9 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -716,7 +742,8 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>TDF, 3TC, DTG, RAL
+```</t>
         </is>
       </c>
     </row>
@@ -734,7 +761,9 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, RAL</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -752,7 +781,9 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -770,7 +801,9 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -788,7 +821,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -806,7 +839,9 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -824,7 +859,9 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>United Kingdom
+```
+```</t>
         </is>
       </c>
     </row>
@@ -842,7 +879,9 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>2017–2020
+```
+```</t>
         </is>
       </c>
     </row>
@@ -860,7 +899,9 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2017–2020</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -878,7 +919,9 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -896,7 +939,9 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -914,7 +959,9 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -932,7 +979,9 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -950,7 +999,9 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>47
+```
+```</t>
         </is>
       </c>
     </row>
@@ -968,7 +1019,9 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -986,7 +1039,9 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI, PI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1059,8 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, PI</t>
+          <t>TDF, FTC, BIC, DRV, DTG, RAL, FTC, TAF, TDF, ABC, 3TC, RPV
+```</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1078,9 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TDF, FTC, BIC, DRV, DTG, RAL, FTC, TAF, TDF, ABC, 3TC, RPV</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1098,9 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1118,9 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1138,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1156,9 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1176,9 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1196,9 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2002-2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1216,9 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2002-2023</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1236,9 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1256,9 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>PBMC
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1276,9 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1296,9 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1316,9 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1336,9 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1356,9 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>All
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1376,8 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>AZT, RTV, ddI, ABC, TDF, LPV/r, ETR, RAL, DRV, DTG, TAF, FTC, BIC, RPV, DOR
+```</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1395,9 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AZT, RTV, ddI, ABC, TDF, LPV/r, ETR, RAL, DRV, DTG, TAF, FTC, BIC, RPV, DOR</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1415,9 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1435,9 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1455,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1473,9 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1493,9 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>Argentina
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1513,9 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>2017–2021
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1533,9 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2017–2021</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1553,9 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1573,9 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1593,9 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1613,9 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1633,9 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1677
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1653,9 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1673,9 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1693,8 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1712,9 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1732,9 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1752,9 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1772,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1790,9 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1810,9 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>Kenya
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1830,9 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>2011–2021
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1850,9 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2011–2021</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1870,9 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1890,9 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1910,9 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1930,9 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1950,9 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>187
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1970,9 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1990,9 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1868,7 +2010,8 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -1886,7 +2029,9 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2049,9 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1922,7 +2069,9 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1940,7 +2089,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2107,9 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN, Pol, Env, Gag
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2127,9 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>South Korea, unspecified Asian and American countries
+```
+```</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2147,9 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>South Korea, unspecified Asian and American countries</t>
+          <t>2021-2024
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2167,9 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2187,9 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2207,9 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol, Env, Gag</t>
+          <t>Plasma or serum
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2227,9 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2247,9 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Plasma or serum</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2267,9 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>487
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2287,9 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2307,9 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2327,8 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2346,9 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2366,9 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2386,9 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2424,9 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PV526713-PV526742</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2444,9 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Brazil
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2464,9 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>2007–2022
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2484,9 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2007–2022</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2504,9 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2524,9 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2544,9 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2564,9 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2584,9 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>30
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2604,9 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2624,9 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2644,8 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir (LPV/r), Efavirenz (EFV)
+```</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2663,9 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir (LPV/r), Efavirenz (EFV)</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2683,9 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2703,9 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2723,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2741,9 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2761,9 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Ghana
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2781,9 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2801,9 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2821,9 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2841,9 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2861,9 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2881,9 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2901,9 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>20
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2921,9 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2941,9 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2961,8 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>NVP, EFV, 3TC, TDF, FTC
+```</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2980,9 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NVP, EFV, 3TC, TDF, FTC</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2768,7 +3000,9 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2786,7 +3020,9 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2804,7 +3040,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2822,7 +3058,9 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2840,7 +3078,9 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>Uganda
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3098,9 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>2021–2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2876,7 +3118,9 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>Sanger sequencing and NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2894,7 +3138,9 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2912,7 +3158,9 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2930,7 +3178,9 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sanger sequencing and NGS</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2948,7 +3198,9 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2966,7 +3218,9 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>295
+```
+```</t>
         </is>
       </c>
     </row>
@@ -2984,7 +3238,9 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3258,9 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3278,8 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Tenofovir (TDF), Lamivudine (3TC), Dolutegravir (DTG), Zidovudine(AZT), Abacavir (ABC), Atazanavir (ATV), Lopinavir/ritonavir (LPVr), Darunavir (DRV)
+```</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3297,9 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tenofovir (TDF), Lamivudine (3TC), Dolutegravir (DTG), Zidovudine(AZT), Abacavir (ABC), Atazanavir (ATV), Lopinavir/ritonavir (LPVr), Darunavir (DRV)</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3317,9 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3337,9 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3357,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3375,9 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3395,9 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3415,9 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3435,9 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3455,9 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3475,9 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3495,9 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3515,9 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3535,9 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2028
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3555,9 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3575,9 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3595,8 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>tenofovir (TFV), INSTIs (integrase strand transfer inhibitors), non-nucleoside reverse transcriptase inhibitors (NNRTIs), protease inhibitors (PIs)
+```</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3614,9 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>tenofovir (TFV), INSTIs (integrase strand transfer inhibitors), non-nucleoside reverse transcriptase inhibitors (NNRTIs), protease inhibitors (PIs)</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3634,9 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3654,9 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3674,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3692,9 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3712,9 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>Malawi
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3732,9 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>2022-2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3752,9 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3772,9 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3792,9 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3812,9 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3832,9 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3852,9 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>213
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3872,9 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3892,9 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3912,8 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NRTI, NRTI, PI, INSTI</t>
+          <t>TDF, 3TC, EFV, DTG
+```</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3931,9 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV, DTG</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3951,9 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3971,9 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3991,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3686,7 +4009,9 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3704,7 +4029,9 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3722,7 +4049,9 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3740,7 +4069,9 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3758,7 +4089,9 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3776,7 +4109,9 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3794,7 +4129,9 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3812,7 +4149,9 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3830,7 +4169,9 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3848,7 +4189,9 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3866,7 +4209,9 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3884,7 +4229,8 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -3902,7 +4248,9 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3920,7 +4268,9 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3938,7 +4288,9 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3974,7 +4326,9 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4346,9 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Tanzania
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4366,9 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4386,9 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4406,9 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4426,9 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4446,9 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4466,9 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4486,9 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>0
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4506,9 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4526,9 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4546,8 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4565,9 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4585,9 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4605,9 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4643,9 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PX133190-PX134237</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4663,9 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>China
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4683,9 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>2019-2022
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4703,9 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2019-2022</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4723,9 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4743,9 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4763,9 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4783,9 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4803,9 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1048
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4823,9 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4843,9 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4863,8 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4882,9 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4902,9 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4922,9 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4960,9 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Pol
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4980,9 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4586,7 +5000,9 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4604,7 +5020,9 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4622,7 +5040,9 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4640,7 +5060,9 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Pol</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4658,7 +5080,9 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4676,7 +5100,9 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4694,7 +5120,9 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4712,7 +5140,9 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4730,7 +5160,9 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4748,7 +5180,8 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Dolutegravir
+```</t>
         </is>
       </c>
     </row>
@@ -4766,7 +5199,9 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Dolutegravir</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4784,7 +5219,9 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4802,7 +5239,9 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4820,7 +5259,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4838,7 +5277,9 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4856,7 +5297,9 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4874,7 +5317,9 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4892,7 +5337,9 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4910,7 +5357,9 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4928,7 +5377,9 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4946,7 +5397,9 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4964,7 +5417,9 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -4982,7 +5437,9 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>24
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5457,9 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5477,9 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5497,8 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5516,9 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5536,9 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5556,9 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5576,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5594,9 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5614,9 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5634,9 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5654,9 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5674,9 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5694,9 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma, PBMC
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5714,9 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5734,9 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5754,9 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>223
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5774,9 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5794,9 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5814,8 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir alafenamide (TAF)
+```</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5833,9 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir alafenamide (TAF)</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5853,9 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5873,9 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5893,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5911,9 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, PR, IN, NC, Env
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5931,9 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>United Kingdom
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5951,9 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>2015–2021
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5971,9 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2015–2021</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5991,9 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5504,7 +6011,9 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>RT, PR, IN, NC, Env</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5522,7 +6031,9 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5540,7 +6051,9 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5558,7 +6071,9 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1182
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5576,7 +6091,9 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5594,7 +6111,9 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5612,7 +6131,8 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -5630,7 +6150,9 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5648,7 +6170,9 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5666,7 +6190,9 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5702,7 +6228,9 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5720,7 +6248,9 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5738,7 +6268,9 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5756,7 +6288,9 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5774,7 +6308,9 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5792,7 +6328,9 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5810,7 +6348,9 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5828,7 +6368,9 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5846,7 +6388,9 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5864,7 +6408,9 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5882,7 +6428,9 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5900,7 +6448,8 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -5918,7 +6467,9 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5936,7 +6487,9 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5954,7 +6507,9 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -5972,7 +6527,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5990,7 +6545,9 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6565,9 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Mozambique
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6585,9 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>2023–2024
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6605,9 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2023–2024</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6625,9 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6645,9 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6665,9 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6685,9 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6705,9 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>28
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6725,9 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6745,9 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6765,8 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Dolutegravir
+```</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6784,9 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Dolutegravir</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6804,9 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6824,9 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6862,9 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>PQ893197, PQ893192, OQ985810, OR259747, PQ893191</t>
+          <t>PR, RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6882,9 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>Cameroon
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6902,9 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>2022-2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6922,9 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6942,9 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6962,9 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6982,9 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6404,7 +7002,9 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6422,7 +7022,9 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>203
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6440,7 +7042,9 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6458,7 +7062,9 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6476,7 +7082,8 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Abacavir (ABC), Lamivudine (3TC), Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Tenofovir (DF/TAF), Atazanavir (ATV), Darunavir (DRV), Dolutegravir (DTG)
+```</t>
         </is>
       </c>
     </row>
@@ -6494,7 +7101,9 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Lamivudine (3TC), Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Tenofovir (DF/TAF), Atazanavir (ATV), Darunavir (DRV), Dolutegravir (DTG)</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6512,7 +7121,9 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6530,7 +7141,9 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6566,7 +7179,9 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6584,7 +7199,9 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>USA, Dominican Republic
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6602,7 +7219,9 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>2019–2020
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6620,7 +7239,9 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2019–2020</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6638,7 +7259,9 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6656,7 +7279,9 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6674,7 +7299,9 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6692,7 +7319,9 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6710,7 +7339,9 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6728,7 +7359,9 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6746,7 +7379,9 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6764,7 +7399,8 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -6782,7 +7418,9 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6800,7 +7438,9 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6818,7 +7458,9 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6854,7 +7496,9 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6872,7 +7516,9 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Uganda
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6890,7 +7536,9 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>2018-2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6908,7 +7556,9 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6926,7 +7576,9 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6944,7 +7596,9 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6962,7 +7616,9 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6980,7 +7636,9 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -6998,7 +7656,9 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>0
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7676,9 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7696,9 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7716,8 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7735,9 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7755,9 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7775,9 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7813,9 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>PV187006</t>
+          <t>All
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7833,9 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>China
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7853,9 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7873,9 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7893,9 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7913,9 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Plasma, Whole Blood
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7933,9 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7953,9 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Plasma, Whole Blood</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7973,9 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7993,9 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7322,7 +8013,9 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7340,7 +8033,8 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>BIC, FTC, TAF
+```</t>
         </is>
       </c>
     </row>
@@ -7358,7 +8052,9 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7376,7 +8072,9 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7394,7 +8092,9 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7430,7 +8130,9 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7448,7 +8150,9 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7466,7 +8170,9 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7484,7 +8190,9 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7502,7 +8210,9 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7520,7 +8230,9 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7538,7 +8250,9 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7556,7 +8270,9 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7574,7 +8290,9 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7592,7 +8310,9 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7610,7 +8330,9 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7628,7 +8350,8 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -7646,7 +8369,9 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7664,7 +8389,9 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7682,7 +8409,9 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7700,7 +8429,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7718,7 +8447,9 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>PQ735970-PQ735985</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7736,7 +8467,9 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>China, United States
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7754,7 +8487,9 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>China, United States</t>
+          <t>1978–2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7772,7 +8507,9 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1978–2023</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7790,7 +8527,9 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7808,7 +8547,9 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7826,7 +8567,9 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7844,7 +8587,9 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7862,7 +8607,9 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7880,7 +8627,9 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7898,7 +8647,9 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7916,7 +8667,8 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -7934,7 +8686,9 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7952,7 +8706,9 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -7970,7 +8726,9 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8764,9 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>PP280627 to PP280757</t>
+          <t>RT
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8784,9 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>Senegal
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8804,9 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>2017–2018
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8824,9 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2017–2018</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8844,9 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8864,9 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Plasma, DBS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8884,9 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8904,9 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Plasma, DBS</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8924,9 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>237
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8944,9 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8964,9 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8984,8 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None
+```</t>
         </is>
       </c>
     </row>
@@ -8222,7 +9003,9 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8240,7 +9023,9 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8258,7 +9043,9 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8276,7 +9063,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8294,7 +9081,9 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8312,7 +9101,9 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>Uganda
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8330,7 +9121,9 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>2021
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8348,7 +9141,9 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Sanger sequencing
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8366,7 +9161,9 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8384,7 +9181,9 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8402,7 +9201,9 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8420,7 +9221,9 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8438,7 +9241,9 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>333
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8456,7 +9261,9 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8474,7 +9281,9 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI,NNRTI, PI,INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8492,7 +9301,8 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI, PI,INSTI</t>
+          <t>Dolutegravir (DTG), Lopinavir (LPV/r), Nevirapine (NVP), Efavirenz (EFV)
+```</t>
         </is>
       </c>
     </row>
@@ -8510,7 +9320,9 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Lopinavir (LPV/r), Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8528,7 +9340,9 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8546,7 +9360,9 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8564,7 +9380,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8582,7 +9398,9 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN, CA
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8600,7 +9418,9 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8618,7 +9438,9 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2021-2023
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8636,7 +9458,9 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2021-2023</t>
+          <t>NGS
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8654,7 +9478,9 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8672,7 +9498,9 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>PR, RT, IN, CA</t>
+          <t>Plasma
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8690,7 +9518,9 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8708,7 +9538,9 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8726,7 +9558,9 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8744,7 +9578,9 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8762,7 +9598,9 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8780,7 +9618,8 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>FTC, TDF, DTG
+```</t>
         </is>
       </c>
     </row>
@@ -8798,7 +9637,9 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>FTC, TDF, DTG</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8816,7 +9657,9 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8834,7 +9677,9 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8870,7 +9715,9 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8888,7 +9735,9 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Kenya, Uganda, Tanzania, Ethiopia
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8906,7 +9755,9 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Kenya, Uganda, Tanzania, Ethiopia</t>
+          <t>2015–2025
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8924,7 +9775,9 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>2015–2025</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8942,7 +9795,9 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not applicable
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8960,7 +9815,9 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8978,7 +9835,9 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -8996,7 +9855,9 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9875,9 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9895,9 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9915,9 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```
+```</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9935,8 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not reported
+```</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9954,9 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No
+```
+```</t>
         </is>
       </c>
     </row>

--- a/advanced-prompting/csv/gpt-4o-mini-2024-07-18_FT-150_PV1_new30.xlsx
+++ b/advanced-prompting/csv/gpt-4o-mini-2024-07-18_FT-150_PV1_new30.xlsx
@@ -464,9 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -484,9 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -522,9 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -542,9 +536,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe
-```
-```</t>
+          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe</t>
         </is>
       </c>
     </row>
@@ -562,9 +554,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2022–2024
-```
-```</t>
+          <t>2022–2024</t>
         </is>
       </c>
     </row>
@@ -582,9 +572,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -602,9 +590,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -622,9 +608,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Plasma, DBS
-```
-```</t>
+          <t>Plasma, DBS</t>
         </is>
       </c>
     </row>
@@ -642,9 +626,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -662,9 +644,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -682,9 +662,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>488
-```
-```</t>
+          <t>488</t>
         </is>
       </c>
     </row>
@@ -702,9 +680,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -722,9 +698,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
     </row>
@@ -742,8 +716,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, RAL
-```</t>
+          <t>TDF, 3TC, DTG, RAL</t>
         </is>
       </c>
     </row>
@@ -761,9 +734,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -781,9 +752,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -801,9 +770,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -839,9 +806,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RT
-```
-```</t>
+          <t>RT</t>
         </is>
       </c>
     </row>
@@ -859,9 +824,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>United Kingdom
-```
-```</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -879,9 +842,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2017–2020
-```
-```</t>
+          <t>2017–2020</t>
         </is>
       </c>
     </row>
@@ -899,9 +860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -919,9 +878,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -939,9 +896,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -959,9 +914,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -979,9 +932,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -999,9 +950,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>47
-```
-```</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -1019,9 +968,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1039,9 +986,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, PI
-```
-```</t>
+          <t>NRTI, INSTI, PI</t>
         </is>
       </c>
     </row>
@@ -1059,8 +1004,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TDF, FTC, BIC, DRV, DTG, RAL, FTC, TAF, TDF, ABC, 3TC, RPV
-```</t>
+          <t>TDF, FTC, BIC, DRV, DTG, RAL, FTC, TAF, TDF, ABC, 3TC, RPV</t>
         </is>
       </c>
     </row>
@@ -1078,9 +1022,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1098,9 +1040,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1118,9 +1058,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1156,9 +1094,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -1176,9 +1112,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -1196,9 +1130,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2002-2023
-```
-```</t>
+          <t>2002-2023</t>
         </is>
       </c>
     </row>
@@ -1216,9 +1148,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -1236,9 +1166,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1256,9 +1184,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PBMC
-```
-```</t>
+          <t>PBMC</t>
         </is>
       </c>
     </row>
@@ -1276,9 +1202,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1296,9 +1220,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1316,9 +1238,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1
-```
-```</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1336,9 +1256,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1356,9 +1274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>All
-```
-```</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -1376,8 +1292,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AZT, RTV, ddI, ABC, TDF, LPV/r, ETR, RAL, DRV, DTG, TAF, FTC, BIC, RPV, DOR
-```</t>
+          <t>AZT, RTV, ddI, ABC, TDF, LPV/r, ETR, RAL, DRV, DTG, TAF, FTC, BIC, RPV, DOR</t>
         </is>
       </c>
     </row>
@@ -1395,9 +1310,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1415,9 +1328,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1435,9 +1346,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1473,9 +1382,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -1493,9 +1400,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Argentina
-```
-```</t>
+          <t>Argentina</t>
         </is>
       </c>
     </row>
@@ -1513,9 +1418,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2017–2021
-```
-```</t>
+          <t>2017–2021</t>
         </is>
       </c>
     </row>
@@ -1533,9 +1436,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -1553,9 +1454,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1573,9 +1472,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -1593,9 +1490,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1613,9 +1508,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1633,9 +1526,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1677
-```
-```</t>
+          <t>1677</t>
         </is>
       </c>
     </row>
@@ -1653,9 +1544,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1673,9 +1562,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1693,8 +1580,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1712,9 +1598,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1732,9 +1616,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1752,9 +1634,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1790,9 +1670,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -1810,9 +1688,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kenya
-```
-```</t>
+          <t>Kenya</t>
         </is>
       </c>
     </row>
@@ -1830,9 +1706,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2011–2021
-```
-```</t>
+          <t>2011–2021</t>
         </is>
       </c>
     </row>
@@ -1850,9 +1724,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -1870,9 +1742,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,9 +1760,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -1910,9 +1778,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1930,9 +1796,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1950,9 +1814,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>187
-```
-```</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -1970,9 +1832,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1990,9 +1850,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI
-```
-```</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
     </row>
@@ -2010,8 +1868,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -2029,9 +1886,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2049,9 +1904,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2069,9 +1922,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2107,9 +1958,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol, Env, Gag
-```
-```</t>
+          <t>PR, RT, IN, Pol, Env, Gag</t>
         </is>
       </c>
     </row>
@@ -2127,9 +1976,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>South Korea, unspecified Asian and American countries
-```
-```</t>
+          <t>South Korea, unspecified Asian and American countries</t>
         </is>
       </c>
     </row>
@@ -2147,9 +1994,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2021-2024
-```
-```</t>
+          <t>2021-2024</t>
         </is>
       </c>
     </row>
@@ -2167,9 +2012,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -2187,9 +2030,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2207,9 +2048,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Plasma or serum
-```
-```</t>
+          <t>Plasma or serum</t>
         </is>
       </c>
     </row>
@@ -2227,9 +2066,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2247,9 +2084,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2267,9 +2102,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>487
-```
-```</t>
+          <t>487</t>
         </is>
       </c>
     </row>
@@ -2287,9 +2120,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2307,9 +2138,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2327,8 +2156,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2346,9 +2174,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2366,9 +2192,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2386,9 +2210,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2424,9 +2246,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -2444,9 +2264,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Brazil
-```
-```</t>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -2464,9 +2282,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2007–2022
-```
-```</t>
+          <t>2007–2022</t>
         </is>
       </c>
     </row>
@@ -2484,9 +2300,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -2504,9 +2318,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2524,9 +2336,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -2544,9 +2354,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2564,9 +2372,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2584,9 +2390,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>30
-```
-```</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -2604,9 +2408,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2624,9 +2426,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -2644,8 +2444,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir (LPV/r), Efavirenz (EFV)
-```</t>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir (LPV/r), Efavirenz (EFV)</t>
         </is>
       </c>
     </row>
@@ -2663,9 +2462,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2683,9 +2480,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2703,9 +2498,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2741,9 +2534,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -2761,9 +2552,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ghana
-```
-```</t>
+          <t>Ghana</t>
         </is>
       </c>
     </row>
@@ -2781,9 +2570,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -2801,9 +2588,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -2821,9 +2606,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2841,9 +2624,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -2861,9 +2642,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2881,9 +2660,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2901,9 +2678,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20
-```
-```</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2921,9 +2696,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2941,9 +2714,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI
-```
-```</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
     </row>
@@ -2961,8 +2732,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NVP, EFV, 3TC, TDF, FTC
-```</t>
+          <t>NVP, EFV, 3TC, TDF, FTC</t>
         </is>
       </c>
     </row>
@@ -2980,9 +2750,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3000,9 +2768,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3020,9 +2786,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3058,9 +2822,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -3078,9 +2840,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Uganda
-```
-```</t>
+          <t>Uganda</t>
         </is>
       </c>
     </row>
@@ -3098,9 +2858,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2021–2023
-```
-```</t>
+          <t>2021–2023</t>
         </is>
       </c>
     </row>
@@ -3118,9 +2876,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sanger sequencing and NGS
-```
-```</t>
+          <t>Sanger sequencing and NGS</t>
         </is>
       </c>
     </row>
@@ -3138,9 +2894,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3158,9 +2912,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -3178,9 +2930,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3198,9 +2948,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3218,9 +2966,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>295
-```
-```</t>
+          <t>295</t>
         </is>
       </c>
     </row>
@@ -3238,9 +2984,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3258,9 +3002,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -3278,8 +3020,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tenofovir (TDF), Lamivudine (3TC), Dolutegravir (DTG), Zidovudine(AZT), Abacavir (ABC), Atazanavir (ATV), Lopinavir/ritonavir (LPVr), Darunavir (DRV)
-```</t>
+          <t>Tenofovir (TDF), Lamivudine (3TC), Dolutegravir (DTG), Zidovudine(AZT), Abacavir (ABC), Atazanavir (ATV), Lopinavir/ritonavir (LPVr), Darunavir (DRV)</t>
         </is>
       </c>
     </row>
@@ -3297,9 +3038,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3317,9 +3056,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3337,9 +3074,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3375,9 +3110,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -3395,9 +3128,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -3415,9 +3146,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -3435,9 +3164,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -3455,9 +3182,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3475,9 +3200,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -3495,9 +3218,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3515,9 +3236,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3535,9 +3254,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2028
-```
-```</t>
+          <t>2028</t>
         </is>
       </c>
     </row>
@@ -3555,9 +3272,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3575,9 +3290,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -3595,8 +3308,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>tenofovir (TFV), INSTIs (integrase strand transfer inhibitors), non-nucleoside reverse transcriptase inhibitors (NNRTIs), protease inhibitors (PIs)
-```</t>
+          <t>tenofovir (TFV), INSTIs (integrase strand transfer inhibitors), non-nucleoside reverse transcriptase inhibitors (NNRTIs), protease inhibitors (PIs)</t>
         </is>
       </c>
     </row>
@@ -3614,9 +3326,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3634,9 +3344,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3654,9 +3362,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3692,9 +3398,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -3712,9 +3416,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Malawi
-```
-```</t>
+          <t>Malawi</t>
         </is>
       </c>
     </row>
@@ -3732,9 +3434,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2022-2023
-```
-```</t>
+          <t>2022-2023</t>
         </is>
       </c>
     </row>
@@ -3752,9 +3452,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -3772,9 +3470,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3792,9 +3488,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -3812,9 +3506,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3832,9 +3524,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3852,9 +3542,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>213
-```
-```</t>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -3872,9 +3560,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3892,9 +3578,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NRTI, NRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -3912,8 +3596,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV, DTG
-```</t>
+          <t>TDF, 3TC, EFV, DTG</t>
         </is>
       </c>
     </row>
@@ -3931,9 +3614,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3951,9 +3632,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3971,9 +3650,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4009,9 +3686,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -4029,9 +3704,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4049,9 +3722,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4069,9 +3740,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -4089,9 +3758,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4109,9 +3776,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -4129,9 +3794,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4149,9 +3812,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4169,9 +3830,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4189,9 +3848,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4209,9 +3866,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4229,8 +3884,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4248,9 +3902,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4268,9 +3920,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4288,9 +3938,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4326,9 +3974,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4346,9 +3992,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Tanzania
-```
-```</t>
+          <t>Tanzania</t>
         </is>
       </c>
     </row>
@@ -4366,9 +4010,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4386,9 +4028,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4406,9 +4046,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4426,9 +4064,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4446,9 +4082,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4466,9 +4100,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4486,9 +4118,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0
-```
-```</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4506,9 +4136,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4526,9 +4154,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4546,8 +4172,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4565,9 +4190,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4585,9 +4208,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4605,9 +4226,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4643,9 +4262,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -4663,9 +4280,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>China
-```
-```</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -4683,9 +4298,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2019-2022
-```
-```</t>
+          <t>2019-2022</t>
         </is>
       </c>
     </row>
@@ -4703,9 +4316,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -4723,9 +4334,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4743,9 +4352,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -4763,9 +4370,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4783,9 +4388,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4803,9 +4406,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>1048
-```
-```</t>
+          <t>1048</t>
         </is>
       </c>
     </row>
@@ -4823,9 +4424,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4843,9 +4442,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4863,8 +4460,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4882,9 +4478,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4902,9 +4496,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4922,9 +4514,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4960,9 +4550,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Pol
-```
-```</t>
+          <t>Pol</t>
         </is>
       </c>
     </row>
@@ -4980,9 +4568,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5000,9 +4586,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5020,9 +4604,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -5040,9 +4622,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5060,9 +4640,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5080,9 +4658,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5100,9 +4676,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5120,9 +4694,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5140,9 +4712,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5160,9 +4730,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5180,8 +4748,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Dolutegravir
-```</t>
+          <t>Dolutegravir</t>
         </is>
       </c>
     </row>
@@ -5199,9 +4766,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5219,9 +4784,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5239,9 +4802,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5277,9 +4838,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -5297,9 +4856,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5317,9 +4874,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5337,9 +4892,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5357,9 +4910,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5377,9 +4928,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -5397,9 +4946,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5417,9 +4964,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5437,9 +4982,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>24
-```
-```</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -5457,9 +5000,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5477,9 +5018,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5497,8 +5036,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5516,9 +5054,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5536,9 +5072,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5556,9 +5090,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5594,9 +5126,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -5614,9 +5144,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5634,9 +5162,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5654,9 +5180,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -5674,9 +5198,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5694,9 +5216,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Plasma, PBMC
-```
-```</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
     </row>
@@ -5714,9 +5234,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5734,9 +5252,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5754,9 +5270,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>223
-```
-```</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -5774,9 +5288,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5794,9 +5306,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
     </row>
@@ -5814,8 +5324,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir alafenamide (TAF)
-```</t>
+          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir alafenamide (TAF)</t>
         </is>
       </c>
     </row>
@@ -5833,9 +5342,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5853,9 +5360,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5873,9 +5378,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5911,9 +5414,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>RT, PR, IN, NC, Env
-```
-```</t>
+          <t>RT, PR, IN, NC, Env</t>
         </is>
       </c>
     </row>
@@ -5931,9 +5432,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>United Kingdom
-```
-```</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -5951,9 +5450,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2015–2021
-```
-```</t>
+          <t>2015–2021</t>
         </is>
       </c>
     </row>
@@ -5971,9 +5468,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5991,9 +5486,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6011,9 +5504,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -6031,9 +5522,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6051,9 +5540,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6071,9 +5558,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1182
-```
-```</t>
+          <t>1182</t>
         </is>
       </c>
     </row>
@@ -6091,9 +5576,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6111,9 +5594,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6131,8 +5612,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6150,9 +5630,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6170,9 +5648,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6190,9 +5666,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6228,9 +5702,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6248,9 +5720,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6268,9 +5738,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6288,9 +5756,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6308,9 +5774,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6328,9 +5792,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6348,9 +5810,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6368,9 +5828,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6388,9 +5846,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6408,9 +5864,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6428,9 +5882,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6448,8 +5900,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6467,9 +5918,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6487,9 +5936,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6507,9 +5954,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6545,9 +5990,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -6565,9 +6008,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Mozambique
-```
-```</t>
+          <t>Mozambique</t>
         </is>
       </c>
     </row>
@@ -6585,9 +6026,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2023–2024
-```
-```</t>
+          <t>2023–2024</t>
         </is>
       </c>
     </row>
@@ -6605,9 +6044,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -6625,9 +6062,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6645,9 +6080,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -6665,9 +6098,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6685,9 +6116,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6705,9 +6134,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>28
-```
-```</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -6725,9 +6152,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6745,9 +6170,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>INSTI
-```
-```</t>
+          <t>INSTI</t>
         </is>
       </c>
     </row>
@@ -6765,8 +6188,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Dolutegravir
-```</t>
+          <t>Dolutegravir</t>
         </is>
       </c>
     </row>
@@ -6784,9 +6206,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6804,9 +6224,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6824,9 +6242,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6862,9 +6278,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -6882,9 +6296,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Cameroon
-```
-```</t>
+          <t>Cameroon</t>
         </is>
       </c>
     </row>
@@ -6902,9 +6314,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2022-2023
-```
-```</t>
+          <t>2022-2023</t>
         </is>
       </c>
     </row>
@@ -6922,9 +6332,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -6942,9 +6350,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6962,9 +6368,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -6982,9 +6386,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7002,9 +6404,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7022,9 +6422,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>203
-```
-```</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -7042,9 +6440,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7062,9 +6458,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI
-```
-```</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
     </row>
@@ -7082,8 +6476,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Lamivudine (3TC), Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Tenofovir (DF/TAF), Atazanavir (ATV), Darunavir (DRV), Dolutegravir (DTG)
-```</t>
+          <t>Abacavir (ABC), Lamivudine (3TC), Efavirenz (EFV), Nevirapine (NVP), Zidovudine (AZT), Tenofovir (DF/TAF), Atazanavir (ATV), Darunavir (DRV), Dolutegravir (DTG)</t>
         </is>
       </c>
     </row>
@@ -7101,9 +6494,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7121,9 +6512,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7141,9 +6530,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7179,9 +6566,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -7199,9 +6584,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic
-```
-```</t>
+          <t>USA, Dominican Republic</t>
         </is>
       </c>
     </row>
@@ -7219,9 +6602,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2019–2020
-```
-```</t>
+          <t>2019–2020</t>
         </is>
       </c>
     </row>
@@ -7239,9 +6620,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7259,9 +6638,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -7279,9 +6656,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7299,9 +6674,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7319,9 +6692,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7339,9 +6710,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>0
-```
-```</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7359,9 +6728,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7379,9 +6746,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7399,8 +6764,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7418,9 +6782,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7438,9 +6800,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7458,9 +6818,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7496,9 +6854,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7516,9 +6872,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Uganda
-```
-```</t>
+          <t>Uganda</t>
         </is>
       </c>
     </row>
@@ -7536,9 +6890,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2018-2023
-```
-```</t>
+          <t>2018-2023</t>
         </is>
       </c>
     </row>
@@ -7556,9 +6908,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7576,9 +6926,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7596,9 +6944,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7616,9 +6962,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7636,9 +6980,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7656,9 +6998,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>0
-```
-```</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7676,9 +7016,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7696,9 +7034,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
     </row>
@@ -7716,8 +7052,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7735,9 +7070,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7755,9 +7088,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7775,9 +7106,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7813,9 +7142,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>All
-```
-```</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -7833,9 +7160,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>China
-```
-```</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -7853,9 +7178,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2023
-```
-```</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7873,9 +7196,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -7893,9 +7214,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7913,9 +7232,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Plasma, Whole Blood
-```
-```</t>
+          <t>Plasma, Whole Blood</t>
         </is>
       </c>
     </row>
@@ -7933,9 +7250,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -7953,9 +7268,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7973,9 +7286,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>1
-```
-```</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7993,9 +7304,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8013,9 +7322,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
     </row>
@@ -8033,8 +7340,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF
-```</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
     </row>
@@ -8052,9 +7358,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8072,9 +7376,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8092,9 +7394,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8130,9 +7430,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8150,9 +7448,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8170,9 +7466,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8190,9 +7484,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8210,9 +7502,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8230,9 +7520,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8250,9 +7538,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8270,9 +7556,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8290,9 +7574,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8310,9 +7592,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8330,9 +7610,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8350,8 +7628,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8369,9 +7646,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8389,9 +7664,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8409,9 +7682,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8447,9 +7718,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8467,9 +7736,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>China, United States
-```
-```</t>
+          <t>China, United States</t>
         </is>
       </c>
     </row>
@@ -8487,9 +7754,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>1978–2023
-```
-```</t>
+          <t>1978–2023</t>
         </is>
       </c>
     </row>
@@ -8507,9 +7772,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -8527,9 +7790,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8547,9 +7808,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -8567,9 +7826,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8587,9 +7844,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8607,9 +7862,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0
-```
-```</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8627,9 +7880,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8647,9 +7898,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8667,8 +7916,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8686,9 +7934,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8706,9 +7952,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8726,9 +7970,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8764,9 +8006,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>RT
-```
-```</t>
+          <t>RT</t>
         </is>
       </c>
     </row>
@@ -8784,9 +8024,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Senegal
-```
-```</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
@@ -8804,9 +8042,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2017–2018
-```
-```</t>
+          <t>2017–2018</t>
         </is>
       </c>
     </row>
@@ -8824,9 +8060,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -8844,9 +8078,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8864,9 +8096,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Plasma, DBS
-```
-```</t>
+          <t>Plasma, DBS</t>
         </is>
       </c>
     </row>
@@ -8884,9 +8114,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8904,9 +8132,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8924,9 +8150,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>237
-```
-```</t>
+          <t>237</t>
         </is>
       </c>
     </row>
@@ -8944,9 +8168,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8964,9 +8186,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8984,8 +8204,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9003,9 +8222,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9023,9 +8240,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9043,9 +8258,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9081,9 +8294,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -9101,9 +8312,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Uganda
-```
-```</t>
+          <t>Uganda</t>
         </is>
       </c>
     </row>
@@ -9121,9 +8330,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2021
-```
-```</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -9141,9 +8348,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -9161,9 +8366,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9181,9 +8384,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -9201,9 +8402,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9221,9 +8420,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9241,9 +8438,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>333
-```
-```</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -9261,9 +8456,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9281,9 +8474,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI, PI,INSTI
-```
-```</t>
+          <t>NRTI,NNRTI, PI,INSTI</t>
         </is>
       </c>
     </row>
@@ -9301,8 +8492,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Lopinavir (LPV/r), Nevirapine (NVP), Efavirenz (EFV)
-```</t>
+          <t>Dolutegravir (DTG), Lopinavir (LPV/r), Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
     </row>
@@ -9320,9 +8510,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9340,9 +8528,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9360,9 +8546,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9398,9 +8582,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>PR, RT, IN, CA
-```
-```</t>
+          <t>PR, RT, IN, CA</t>
         </is>
       </c>
     </row>
@@ -9418,9 +8600,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9438,9 +8618,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2021-2023
-```
-```</t>
+          <t>2021-2023</t>
         </is>
       </c>
     </row>
@@ -9458,9 +8636,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
     </row>
@@ -9478,9 +8654,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9498,9 +8672,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -9518,9 +8690,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9538,9 +8708,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9558,9 +8726,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9578,9 +8744,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9598,9 +8762,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
     </row>
@@ -9618,8 +8780,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>FTC, TDF, DTG
-```</t>
+          <t>FTC, TDF, DTG</t>
         </is>
       </c>
     </row>
@@ -9637,9 +8798,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9657,9 +8816,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9677,9 +8834,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9715,9 +8870,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -9735,9 +8888,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Kenya, Uganda, Tanzania, Ethiopia
-```
-```</t>
+          <t>Kenya, Uganda, Tanzania, Ethiopia</t>
         </is>
       </c>
     </row>
@@ -9755,9 +8906,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>2015–2025
-```
-```</t>
+          <t>2015–2025</t>
         </is>
       </c>
     </row>
@@ -9775,9 +8924,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9795,9 +8942,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -9815,9 +8960,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9835,9 +8978,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9855,9 +8996,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9875,9 +9014,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9895,9 +9032,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9915,9 +9050,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9935,8 +9068,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9954,9 +9086,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
     </row>
